--- a/output/yearly_population_iteration_15_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_15_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4747</v>
+        <v>5463</v>
       </c>
       <c r="C2" t="n">
-        <v>10372</v>
+        <v>10093</v>
       </c>
       <c r="D2" t="n">
-        <v>29902</v>
+        <v>30478</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3419</v>
+        <v>3878</v>
       </c>
       <c r="C3" t="n">
-        <v>10477</v>
+        <v>9678</v>
       </c>
       <c r="D3" t="n">
-        <v>15808</v>
+        <v>15635</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2624</v>
+        <v>3023</v>
       </c>
       <c r="C4" t="n">
-        <v>8431</v>
+        <v>6744</v>
       </c>
       <c r="D4" t="n">
-        <v>7756</v>
+        <v>7365</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1724</v>
+        <v>1877</v>
       </c>
       <c r="C5" t="n">
-        <v>7026</v>
+        <v>5540</v>
       </c>
       <c r="D5" t="n">
-        <v>3000</v>
+        <v>2672</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>958</v>
+        <v>1008</v>
       </c>
       <c r="C6" t="n">
-        <v>4054</v>
+        <v>3654</v>
       </c>
       <c r="D6" t="n">
-        <v>1167</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>460</v>
+        <v>444</v>
       </c>
       <c r="C7" t="n">
-        <v>2112</v>
+        <v>2167</v>
       </c>
       <c r="D7" t="n">
-        <v>654</v>
+        <v>647</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="C8" t="n">
-        <v>875</v>
+        <v>1038</v>
       </c>
       <c r="D8" t="n">
-        <v>426</v>
+        <v>435</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>342</v>
+        <v>431</v>
       </c>
       <c r="D9" t="n">
-        <v>308</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>206</v>
+        <v>225</v>
       </c>
       <c r="D10" t="n">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11">
@@ -906,10 +906,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D11" t="n">
         <v>203</v>
@@ -923,7 +923,7 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D12" t="n">
         <v>160</v>
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -965,7 +965,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
         <v>82</v>
@@ -982,7 +982,7 @@
         <v>45</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -1007,7 +1007,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1024,7 +1024,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6763</v>
+        <v>6713</v>
       </c>
       <c r="C2" t="n">
-        <v>6875</v>
+        <v>16196</v>
       </c>
       <c r="D2" t="n">
-        <v>24815</v>
+        <v>34050</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3257</v>
+        <v>3719</v>
       </c>
       <c r="C3" t="n">
-        <v>9248</v>
+        <v>8719</v>
       </c>
       <c r="D3" t="n">
-        <v>16575</v>
+        <v>16509</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2544</v>
+        <v>2885</v>
       </c>
       <c r="C4" t="n">
-        <v>9078</v>
+        <v>7862</v>
       </c>
       <c r="D4" t="n">
-        <v>8757</v>
+        <v>8340</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1846</v>
+        <v>2071</v>
       </c>
       <c r="C5" t="n">
-        <v>7419</v>
+        <v>5956</v>
       </c>
       <c r="D5" t="n">
-        <v>3564</v>
+        <v>3311</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1148</v>
+        <v>1237</v>
       </c>
       <c r="C6" t="n">
-        <v>5272</v>
+        <v>4381</v>
       </c>
       <c r="D6" t="n">
-        <v>1415</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="C7" t="n">
-        <v>2889</v>
+        <v>2771</v>
       </c>
       <c r="D7" t="n">
-        <v>711</v>
+        <v>713</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="C8" t="n">
-        <v>1371</v>
+        <v>1502</v>
       </c>
       <c r="D8" t="n">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C9" t="n">
-        <v>542</v>
+        <v>664</v>
       </c>
       <c r="D9" t="n">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -1206,7 +1206,7 @@
         <v>43</v>
       </c>
       <c r="C10" t="n">
-        <v>254</v>
+        <v>303</v>
       </c>
       <c r="D10" t="n">
         <v>247</v>
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -1237,7 +1237,7 @@
         <v>137</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -1279,7 +1279,7 @@
         <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -1318,7 +1318,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1335,7 +1335,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7200</v>
+        <v>7292</v>
       </c>
       <c r="C2" t="n">
-        <v>7491</v>
+        <v>13421</v>
       </c>
       <c r="D2" t="n">
-        <v>19575</v>
+        <v>30348</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3697</v>
+        <v>3939</v>
       </c>
       <c r="C3" t="n">
-        <v>7459</v>
+        <v>10426</v>
       </c>
       <c r="D3" t="n">
-        <v>16463</v>
+        <v>17443</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2401</v>
+        <v>2731</v>
       </c>
       <c r="C4" t="n">
-        <v>8957</v>
+        <v>7968</v>
       </c>
       <c r="D4" t="n">
-        <v>9457</v>
+        <v>9104</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1879</v>
+        <v>2117</v>
       </c>
       <c r="C5" t="n">
-        <v>7830</v>
+        <v>6525</v>
       </c>
       <c r="D5" t="n">
-        <v>4153</v>
+        <v>3854</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1294</v>
+        <v>1408</v>
       </c>
       <c r="C6" t="n">
-        <v>5980</v>
+        <v>4906</v>
       </c>
       <c r="D6" t="n">
-        <v>1651</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>710</v>
+        <v>752</v>
       </c>
       <c r="C7" t="n">
-        <v>3746</v>
+        <v>3385</v>
       </c>
       <c r="D7" t="n">
-        <v>793</v>
+        <v>778</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C8" t="n">
-        <v>1920</v>
+        <v>1946</v>
       </c>
       <c r="D8" t="n">
-        <v>473</v>
+        <v>483</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C9" t="n">
-        <v>820</v>
+        <v>952</v>
       </c>
       <c r="D9" t="n">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="10">
@@ -1514,10 +1514,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C10" t="n">
-        <v>347</v>
+        <v>423</v>
       </c>
       <c r="D10" t="n">
         <v>252</v>
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -1548,7 +1548,7 @@
         <v>150</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -1562,7 +1562,7 @@
         <v>114</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -1590,7 +1590,7 @@
         <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -1629,7 +1629,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1646,7 +1646,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6679</v>
+        <v>6780</v>
       </c>
       <c r="C2" t="n">
-        <v>5333</v>
+        <v>9448</v>
       </c>
       <c r="D2" t="n">
-        <v>16608</v>
+        <v>25283</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4282</v>
+        <v>4743</v>
       </c>
       <c r="C3" t="n">
-        <v>11775</v>
+        <v>14816</v>
       </c>
       <c r="D3" t="n">
-        <v>17852</v>
+        <v>18624</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1736</v>
+        <v>1956</v>
       </c>
       <c r="C4" t="n">
-        <v>12160</v>
+        <v>10394</v>
       </c>
       <c r="D4" t="n">
-        <v>8993</v>
+        <v>8556</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1195</v>
+        <v>1300</v>
       </c>
       <c r="C5" t="n">
-        <v>5860</v>
+        <v>4807</v>
       </c>
       <c r="D5" t="n">
-        <v>2694</v>
+        <v>2552</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>656</v>
+        <v>694</v>
       </c>
       <c r="C6" t="n">
-        <v>3671</v>
+        <v>3317</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>762</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C7" t="n">
-        <v>1881</v>
+        <v>1907</v>
       </c>
       <c r="D7" t="n">
-        <v>463</v>
+        <v>473</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C8" t="n">
-        <v>803</v>
+        <v>932</v>
       </c>
       <c r="D8" t="n">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="9">
@@ -1814,7 +1814,7 @@
         <v>48</v>
       </c>
       <c r="C9" t="n">
-        <v>340</v>
+        <v>414</v>
       </c>
       <c r="D9" t="n">
         <v>246</v>
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>196</v>
+        <v>217</v>
       </c>
       <c r="D10" t="n">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11">
@@ -1845,7 +1845,7 @@
         <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12">
@@ -1859,7 +1859,7 @@
         <v>111</v>
       </c>
       <c r="D12" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
@@ -1887,7 +1887,7 @@
         <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16">
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D17" t="n">
         <v>38</v>
@@ -1943,7 +1943,7 @@
         <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4204</v>
+        <v>4161</v>
       </c>
       <c r="C2" t="n">
-        <v>4125</v>
+        <v>4665</v>
       </c>
       <c r="D2" t="n">
-        <v>11801</v>
+        <v>17916</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4511</v>
+        <v>4809</v>
       </c>
       <c r="C3" t="n">
-        <v>8194</v>
+        <v>11384</v>
       </c>
       <c r="D3" t="n">
-        <v>16693</v>
+        <v>18433</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2306</v>
+        <v>2576</v>
       </c>
       <c r="C4" t="n">
-        <v>12204</v>
+        <v>12529</v>
       </c>
       <c r="D4" t="n">
-        <v>10167</v>
+        <v>9909</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1322</v>
+        <v>1452</v>
       </c>
       <c r="C5" t="n">
-        <v>8382</v>
+        <v>7037</v>
       </c>
       <c r="D5" t="n">
-        <v>3389</v>
+        <v>3215</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>763</v>
+        <v>809</v>
       </c>
       <c r="C6" t="n">
-        <v>4610</v>
+        <v>4006</v>
       </c>
       <c r="D6" t="n">
-        <v>956</v>
+        <v>929</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C7" t="n">
-        <v>2466</v>
+        <v>2401</v>
       </c>
       <c r="D7" t="n">
-        <v>507</v>
+        <v>516</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C8" t="n">
-        <v>1088</v>
+        <v>1221</v>
       </c>
       <c r="D8" t="n">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="9">
@@ -2125,10 +2125,10 @@
         <v>39</v>
       </c>
       <c r="C9" t="n">
-        <v>365</v>
+        <v>442</v>
       </c>
       <c r="D9" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="D10" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11">
@@ -2156,7 +2156,7 @@
         <v>162</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="12">
@@ -2184,7 +2184,7 @@
         <v>63</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15">
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D16" t="n">
         <v>37</v>
@@ -2240,7 +2240,7 @@
         <v>29</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4585</v>
+        <v>3695</v>
       </c>
       <c r="C2" t="n">
-        <v>5750</v>
+        <v>5028</v>
       </c>
       <c r="D2" t="n">
-        <v>13871</v>
+        <v>21208</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3689</v>
+        <v>3830</v>
       </c>
       <c r="C3" t="n">
-        <v>5707</v>
+        <v>7511</v>
       </c>
       <c r="D3" t="n">
-        <v>15066</v>
+        <v>17300</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2756</v>
+        <v>3002</v>
       </c>
       <c r="C4" t="n">
-        <v>10102</v>
+        <v>11740</v>
       </c>
       <c r="D4" t="n">
-        <v>10860</v>
+        <v>10917</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1513</v>
+        <v>1675</v>
       </c>
       <c r="C5" t="n">
-        <v>9895</v>
+        <v>9315</v>
       </c>
       <c r="D5" t="n">
-        <v>4262</v>
+        <v>4050</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>908</v>
+        <v>979</v>
       </c>
       <c r="C6" t="n">
-        <v>6206</v>
+        <v>5288</v>
       </c>
       <c r="D6" t="n">
-        <v>1270</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>401</v>
+        <v>413</v>
       </c>
       <c r="C7" t="n">
-        <v>3326</v>
+        <v>3044</v>
       </c>
       <c r="D7" t="n">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C8" t="n">
-        <v>1624</v>
+        <v>1683</v>
       </c>
       <c r="D8" t="n">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="9">
@@ -2436,10 +2436,10 @@
         <v>49</v>
       </c>
       <c r="C9" t="n">
-        <v>623</v>
+        <v>720</v>
       </c>
       <c r="D9" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>268</v>
+        <v>302</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12">
@@ -2495,7 +2495,7 @@
         <v>70</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D16" t="n">
         <v>36</v>
@@ -2551,7 +2551,7 @@
         <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2800</v>
+        <v>2276</v>
       </c>
       <c r="C2" t="n">
-        <v>2826</v>
+        <v>2486</v>
       </c>
       <c r="D2" t="n">
-        <v>9814</v>
+        <v>14979</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3750</v>
+        <v>3672</v>
       </c>
       <c r="C3" t="n">
-        <v>5574</v>
+        <v>6544</v>
       </c>
       <c r="D3" t="n">
-        <v>14637</v>
+        <v>17315</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3015</v>
+        <v>3272</v>
       </c>
       <c r="C4" t="n">
-        <v>9553</v>
+        <v>11364</v>
       </c>
       <c r="D4" t="n">
-        <v>11455</v>
+        <v>11677</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1563</v>
+        <v>1716</v>
       </c>
       <c r="C5" t="n">
-        <v>11543</v>
+        <v>11319</v>
       </c>
       <c r="D5" t="n">
-        <v>4367</v>
+        <v>4166</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>722</v>
+        <v>761</v>
       </c>
       <c r="C6" t="n">
-        <v>7021</v>
+        <v>5990</v>
       </c>
       <c r="D6" t="n">
-        <v>1237</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C7" t="n">
-        <v>3248</v>
+        <v>3110</v>
       </c>
       <c r="D7" t="n">
-        <v>557</v>
+        <v>568</v>
       </c>
     </row>
     <row r="8">
@@ -2733,10 +2733,10 @@
         <v>45</v>
       </c>
       <c r="C8" t="n">
-        <v>1072</v>
+        <v>1183</v>
       </c>
       <c r="D8" t="n">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>262</v>
+        <v>295</v>
       </c>
       <c r="D9" t="n">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="D10" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11">
@@ -2792,7 +2792,7 @@
         <v>68</v>
       </c>
       <c r="D12" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14">
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D15" t="n">
         <v>35</v>
@@ -2848,7 +2848,7 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3118</v>
+        <v>2742</v>
       </c>
       <c r="C2" t="n">
-        <v>4946</v>
+        <v>5229</v>
       </c>
       <c r="D2" t="n">
-        <v>12063</v>
+        <v>11943</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2886</v>
+        <v>2662</v>
       </c>
       <c r="C3" t="n">
-        <v>3952</v>
+        <v>4327</v>
       </c>
       <c r="D3" t="n">
-        <v>13059</v>
+        <v>16046</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2903</v>
+        <v>3025</v>
       </c>
       <c r="C4" t="n">
-        <v>7597</v>
+        <v>8999</v>
       </c>
       <c r="D4" t="n">
-        <v>11705</v>
+        <v>12133</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1873</v>
+        <v>2045</v>
       </c>
       <c r="C5" t="n">
-        <v>10573</v>
+        <v>11211</v>
       </c>
       <c r="D5" t="n">
-        <v>5186</v>
+        <v>5048</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>919</v>
+        <v>987</v>
       </c>
       <c r="C6" t="n">
-        <v>8809</v>
+        <v>8094</v>
       </c>
       <c r="D6" t="n">
-        <v>1611</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="C7" t="n">
-        <v>4715</v>
+        <v>4242</v>
       </c>
       <c r="D7" t="n">
-        <v>636</v>
+        <v>644</v>
       </c>
     </row>
     <row r="8">
@@ -3044,10 +3044,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>1817</v>
+        <v>1847</v>
       </c>
       <c r="D8" t="n">
-        <v>380</v>
+        <v>387</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>507</v>
+        <v>564</v>
       </c>
       <c r="D9" t="n">
-        <v>290</v>
+        <v>287</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="D10" t="n">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="11">
@@ -3086,7 +3086,7 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D11" t="n">
         <v>133</v>
@@ -3103,7 +3103,7 @@
         <v>78</v>
       </c>
       <c r="D12" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14">
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D15" t="n">
         <v>33</v>
@@ -3159,7 +3159,7 @@
         <v>58</v>
       </c>
       <c r="D16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2043</v>
+        <v>1893</v>
       </c>
       <c r="C2" t="n">
-        <v>3645</v>
+        <v>3472</v>
       </c>
       <c r="D2" t="n">
-        <v>9616</v>
+        <v>10139</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2593</v>
+        <v>2357</v>
       </c>
       <c r="C3" t="n">
-        <v>3976</v>
+        <v>4249</v>
       </c>
       <c r="D3" t="n">
-        <v>12257</v>
+        <v>14739</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2667</v>
+        <v>2674</v>
       </c>
       <c r="C4" t="n">
-        <v>6220</v>
+        <v>7321</v>
       </c>
       <c r="D4" t="n">
-        <v>11630</v>
+        <v>12485</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2052</v>
+        <v>2216</v>
       </c>
       <c r="C5" t="n">
-        <v>9759</v>
+        <v>10578</v>
       </c>
       <c r="D5" t="n">
-        <v>5816</v>
+        <v>5623</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1046</v>
+        <v>1125</v>
       </c>
       <c r="C6" t="n">
-        <v>9677</v>
+        <v>9308</v>
       </c>
       <c r="D6" t="n">
-        <v>1898</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="C7" t="n">
-        <v>5919</v>
+        <v>5361</v>
       </c>
       <c r="D7" t="n">
-        <v>717</v>
+        <v>723</v>
       </c>
     </row>
     <row r="8">
@@ -3355,10 +3355,10 @@
         <v>46</v>
       </c>
       <c r="C8" t="n">
-        <v>2380</v>
+        <v>2352</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>392</v>
       </c>
     </row>
     <row r="9">
@@ -3369,10 +3369,10 @@
         <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>545</v>
+        <v>600</v>
       </c>
       <c r="D9" t="n">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10">
@@ -3380,10 +3380,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="D10" t="n">
         <v>174</v>
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D12" t="n">
         <v>90</v>
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D14" t="n">
         <v>36</v>
@@ -3456,7 +3456,7 @@
         <v>56</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2964</v>
+        <v>2834</v>
       </c>
       <c r="C2" t="n">
-        <v>8358</v>
+        <v>8393</v>
       </c>
       <c r="D2" t="n">
-        <v>18152</v>
+        <v>16433</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2035</v>
+        <v>1860</v>
       </c>
       <c r="C3" t="n">
-        <v>3476</v>
+        <v>3545</v>
       </c>
       <c r="D3" t="n">
-        <v>11196</v>
+        <v>13304</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2296</v>
+        <v>2234</v>
       </c>
       <c r="C4" t="n">
-        <v>5207</v>
+        <v>5959</v>
       </c>
       <c r="D4" t="n">
-        <v>11360</v>
+        <v>12408</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2050</v>
+        <v>2180</v>
       </c>
       <c r="C5" t="n">
-        <v>8231</v>
+        <v>9138</v>
       </c>
       <c r="D5" t="n">
-        <v>6364</v>
+        <v>6308</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1265</v>
+        <v>1342</v>
       </c>
       <c r="C6" t="n">
-        <v>9630</v>
+        <v>9686</v>
       </c>
       <c r="D6" t="n">
-        <v>2306</v>
+        <v>2261</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>418</v>
+        <v>441</v>
       </c>
       <c r="C7" t="n">
-        <v>7205</v>
+        <v>6712</v>
       </c>
       <c r="D7" t="n">
-        <v>848</v>
+        <v>830</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C8" t="n">
-        <v>3523</v>
+        <v>3347</v>
       </c>
       <c r="D8" t="n">
-        <v>416</v>
+        <v>423</v>
       </c>
     </row>
     <row r="9">
@@ -3680,10 +3680,10 @@
         <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>1107</v>
+        <v>1114</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>302</v>
+        <v>324</v>
       </c>
       <c r="D10" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3725,7 +3725,7 @@
         <v>84</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D13" t="n">
         <v>62</v>
@@ -3767,7 +3767,7 @@
         <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5853</v>
+        <v>4954</v>
       </c>
       <c r="C2" t="n">
-        <v>5103</v>
+        <v>11339</v>
       </c>
       <c r="D2" t="n">
-        <v>4975</v>
+        <v>13386</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2188</v>
+        <v>2093</v>
       </c>
       <c r="C2" t="n">
-        <v>5014</v>
+        <v>5035</v>
       </c>
       <c r="D2" t="n">
-        <v>13506</v>
+        <v>12357</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2705</v>
+        <v>2527</v>
       </c>
       <c r="C3" t="n">
-        <v>4874</v>
+        <v>4957</v>
       </c>
       <c r="D3" t="n">
-        <v>12637</v>
+        <v>14513</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3067</v>
+        <v>3156</v>
       </c>
       <c r="C4" t="n">
-        <v>7897</v>
+        <v>9002</v>
       </c>
       <c r="D4" t="n">
-        <v>11621</v>
+        <v>12533</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1168</v>
+        <v>1240</v>
       </c>
       <c r="C5" t="n">
-        <v>12969</v>
+        <v>13492</v>
       </c>
       <c r="D5" t="n">
-        <v>5673</v>
+        <v>5611</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>386</v>
+        <v>407</v>
       </c>
       <c r="C6" t="n">
-        <v>8665</v>
+        <v>8191</v>
       </c>
       <c r="D6" t="n">
-        <v>1838</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C7" t="n">
-        <v>3452</v>
+        <v>3280</v>
       </c>
       <c r="D7" t="n">
-        <v>507</v>
+        <v>512</v>
       </c>
     </row>
     <row r="8">
@@ -4288,10 +4288,10 @@
         <v>17</v>
       </c>
       <c r="C8" t="n">
-        <v>1084</v>
+        <v>1091</v>
       </c>
       <c r="D8" t="n">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>295</v>
+        <v>317</v>
       </c>
       <c r="D9" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D10" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11">
@@ -4333,7 +4333,7 @@
         <v>82</v>
       </c>
       <c r="D11" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12">
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D12" t="n">
         <v>60</v>
@@ -4375,7 +4375,7 @@
         <v>58</v>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7039</v>
+        <v>6791</v>
       </c>
       <c r="C2" t="n">
-        <v>10189</v>
+        <v>4632</v>
       </c>
       <c r="D2" t="n">
-        <v>21160</v>
+        <v>12839</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2487</v>
+        <v>2106</v>
       </c>
       <c r="C3" t="n">
-        <v>2612</v>
+        <v>5714</v>
       </c>
       <c r="D3" t="n">
-        <v>1514</v>
+        <v>2888</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>816</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
@@ -4655,7 +4655,7 @@
         <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D12" t="n">
         <v>199</v>
@@ -4669,7 +4669,7 @@
         <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D13" t="n">
         <v>170</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4316</v>
+        <v>4909</v>
       </c>
       <c r="C2" t="n">
-        <v>8308</v>
+        <v>6483</v>
       </c>
       <c r="D2" t="n">
-        <v>28766</v>
+        <v>19402</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3910</v>
+        <v>3649</v>
       </c>
       <c r="C3" t="n">
-        <v>5950</v>
+        <v>4399</v>
       </c>
       <c r="D3" t="n">
-        <v>4703</v>
+        <v>4347</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1114</v>
+        <v>949</v>
       </c>
       <c r="C4" t="n">
-        <v>1574</v>
+        <v>3392</v>
       </c>
       <c r="D4" t="n">
-        <v>1486</v>
+        <v>1763</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>859</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -4921,7 +4921,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9" t="n">
         <v>232</v>
@@ -4935,10 +4935,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
         <v>352</v>
@@ -4952,7 +4952,7 @@
         <v>43</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4994,7 +4994,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D14" t="n">
         <v>146</v>
@@ -5022,7 +5022,7 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>98</v>
@@ -5036,7 +5036,7 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D17" t="n">
         <v>78</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4866</v>
+        <v>5411</v>
       </c>
       <c r="C2" t="n">
-        <v>9212</v>
+        <v>10862</v>
       </c>
       <c r="D2" t="n">
-        <v>31303</v>
+        <v>19254</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3390</v>
+        <v>3509</v>
       </c>
       <c r="C3" t="n">
-        <v>6263</v>
+        <v>4791</v>
       </c>
       <c r="D3" t="n">
-        <v>8214</v>
+        <v>6442</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2135</v>
+        <v>1951</v>
       </c>
       <c r="C4" t="n">
-        <v>4019</v>
+        <v>3891</v>
       </c>
       <c r="D4" t="n">
-        <v>2058</v>
+        <v>2205</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>507</v>
+        <v>442</v>
       </c>
       <c r="C5" t="n">
-        <v>955</v>
+        <v>1951</v>
       </c>
       <c r="D5" t="n">
-        <v>1193</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>908</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D7" t="n">
-        <v>631</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D8" t="n">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -5238,7 +5238,7 @@
         <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C11" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5277,7 +5277,7 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D12" t="n">
         <v>213</v>
@@ -5319,7 +5319,7 @@
         <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
         <v>120</v>
@@ -5333,7 +5333,7 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5119</v>
+        <v>6751</v>
       </c>
       <c r="C2" t="n">
-        <v>13984</v>
+        <v>8659</v>
       </c>
       <c r="D2" t="n">
-        <v>28379</v>
+        <v>34124</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3350</v>
+        <v>3605</v>
       </c>
       <c r="C3" t="n">
-        <v>6772</v>
+        <v>6889</v>
       </c>
       <c r="D3" t="n">
-        <v>11145</v>
+        <v>7935</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2329</v>
+        <v>2289</v>
       </c>
       <c r="C4" t="n">
-        <v>5141</v>
+        <v>4293</v>
       </c>
       <c r="D4" t="n">
-        <v>3118</v>
+        <v>2910</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1085</v>
+        <v>980</v>
       </c>
       <c r="C5" t="n">
-        <v>2523</v>
+        <v>2916</v>
       </c>
       <c r="D5" t="n">
-        <v>1294</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>280</v>
+        <v>254</v>
       </c>
       <c r="C6" t="n">
-        <v>622</v>
+        <v>1120</v>
       </c>
       <c r="D6" t="n">
-        <v>946</v>
+        <v>955</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D7" t="n">
-        <v>664</v>
+        <v>660</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C8" t="n">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D8" t="n">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="9">
@@ -5549,7 +5549,7 @@
         <v>306</v>
       </c>
       <c r="D9" t="n">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10">
@@ -5557,10 +5557,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D10" t="n">
         <v>342</v>
@@ -5571,7 +5571,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C11" t="n">
         <v>189</v>
@@ -5588,7 +5588,7 @@
         <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D12" t="n">
         <v>217</v>
@@ -5630,7 +5630,7 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D15" t="n">
         <v>122</v>
@@ -5658,7 +5658,7 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
         <v>79</v>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6789</v>
+        <v>6985</v>
       </c>
       <c r="C2" t="n">
-        <v>15735</v>
+        <v>11276</v>
       </c>
       <c r="D2" t="n">
-        <v>26974</v>
+        <v>31110</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3083</v>
+        <v>3693</v>
       </c>
       <c r="C3" t="n">
-        <v>8514</v>
+        <v>6374</v>
       </c>
       <c r="D3" t="n">
-        <v>12211</v>
+        <v>10683</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1741</v>
+        <v>1804</v>
       </c>
       <c r="C4" t="n">
-        <v>4889</v>
+        <v>4630</v>
       </c>
       <c r="D4" t="n">
-        <v>3918</v>
+        <v>3260</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>885</v>
+        <v>842</v>
       </c>
       <c r="C5" t="n">
-        <v>2836</v>
+        <v>2648</v>
       </c>
       <c r="D5" t="n">
-        <v>1261</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>321</v>
+        <v>290</v>
       </c>
       <c r="C6" t="n">
-        <v>1050</v>
+        <v>1352</v>
       </c>
       <c r="D6" t="n">
-        <v>765</v>
+        <v>780</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C7" t="n">
-        <v>306</v>
+        <v>457</v>
       </c>
       <c r="D7" t="n">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D8" t="n">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9">
@@ -5860,7 +5860,7 @@
         <v>196</v>
       </c>
       <c r="D9" t="n">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10">
@@ -5871,7 +5871,7 @@
         <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
         <v>233</v>
@@ -5899,7 +5899,7 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D12" t="n">
         <v>147</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4802</v>
+        <v>5913</v>
       </c>
       <c r="C2" t="n">
-        <v>8608</v>
+        <v>8650</v>
       </c>
       <c r="D2" t="n">
-        <v>24680</v>
+        <v>28663</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4085</v>
+        <v>4416</v>
       </c>
       <c r="C3" t="n">
-        <v>10910</v>
+        <v>7918</v>
       </c>
       <c r="D3" t="n">
-        <v>13792</v>
+        <v>13328</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2107</v>
+        <v>2404</v>
       </c>
       <c r="C4" t="n">
-        <v>6944</v>
+        <v>5571</v>
       </c>
       <c r="D4" t="n">
-        <v>5470</v>
+        <v>4657</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="C5" t="n">
-        <v>3959</v>
+        <v>3709</v>
       </c>
       <c r="D5" t="n">
-        <v>1720</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>549</v>
+        <v>523</v>
       </c>
       <c r="C6" t="n">
-        <v>2031</v>
+        <v>2069</v>
       </c>
       <c r="D6" t="n">
-        <v>849</v>
+        <v>864</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>186</v>
+        <v>169</v>
       </c>
       <c r="C7" t="n">
-        <v>711</v>
+        <v>956</v>
       </c>
       <c r="D7" t="n">
-        <v>556</v>
+        <v>553</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C8" t="n">
-        <v>268</v>
+        <v>349</v>
       </c>
       <c r="D8" t="n">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10">
@@ -6182,7 +6182,7 @@
         <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D10" t="n">
         <v>235</v>
@@ -6193,7 +6193,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C11" t="n">
         <v>131</v>
@@ -6210,7 +6210,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
         <v>153</v>
@@ -6224,7 +6224,7 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
         <v>119</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4787</v>
+        <v>5290</v>
       </c>
       <c r="C2" t="n">
-        <v>15655</v>
+        <v>15277</v>
       </c>
       <c r="D2" t="n">
-        <v>31424</v>
+        <v>28110</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3650</v>
+        <v>4227</v>
       </c>
       <c r="C3" t="n">
-        <v>8428</v>
+        <v>7212</v>
       </c>
       <c r="D3" t="n">
-        <v>14476</v>
+        <v>14720</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2605</v>
+        <v>2911</v>
       </c>
       <c r="C4" t="n">
-        <v>8969</v>
+        <v>6685</v>
       </c>
       <c r="D4" t="n">
-        <v>6769</v>
+        <v>6052</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1429</v>
+        <v>1534</v>
       </c>
       <c r="C5" t="n">
-        <v>5452</v>
+        <v>4632</v>
       </c>
       <c r="D5" t="n">
-        <v>2351</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="C6" t="n">
-        <v>2969</v>
+        <v>2896</v>
       </c>
       <c r="D6" t="n">
-        <v>979</v>
+        <v>972</v>
       </c>
     </row>
     <row r="7">
@@ -6448,10 +6448,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>319</v>
+        <v>298</v>
       </c>
       <c r="C7" t="n">
-        <v>1383</v>
+        <v>1522</v>
       </c>
       <c r="D7" t="n">
         <v>602</v>
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C8" t="n">
-        <v>484</v>
+        <v>642</v>
       </c>
       <c r="D8" t="n">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>235</v>
+        <v>276</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10">
@@ -6490,7 +6490,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" t="n">
         <v>189</v>
@@ -6507,7 +6507,7 @@
         <v>24</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
         <v>200</v>
@@ -6535,10 +6535,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -6563,7 +6563,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D15" t="n">
         <v>81</v>
@@ -6577,7 +6577,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D16" t="n">
         <v>63</v>

--- a/output/yearly_population_iteration_15_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_15_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5463</v>
+        <v>3725</v>
       </c>
       <c r="C2" t="n">
-        <v>10093</v>
+        <v>11187</v>
       </c>
       <c r="D2" t="n">
-        <v>30478</v>
+        <v>32046</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3878</v>
+        <v>2816</v>
       </c>
       <c r="C3" t="n">
-        <v>9678</v>
+        <v>6135</v>
       </c>
       <c r="D3" t="n">
-        <v>15635</v>
+        <v>20566</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3023</v>
+        <v>2313</v>
       </c>
       <c r="C4" t="n">
-        <v>6744</v>
+        <v>4272</v>
       </c>
       <c r="D4" t="n">
-        <v>7365</v>
+        <v>9897</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1877</v>
+        <v>1521</v>
       </c>
       <c r="C5" t="n">
-        <v>5540</v>
+        <v>4085</v>
       </c>
       <c r="D5" t="n">
-        <v>2672</v>
+        <v>3761</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1008</v>
+        <v>846</v>
       </c>
       <c r="C6" t="n">
-        <v>3654</v>
+        <v>2914</v>
       </c>
       <c r="D6" t="n">
-        <v>1145</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>444</v>
+        <v>400</v>
       </c>
       <c r="C7" t="n">
-        <v>2167</v>
+        <v>1525</v>
       </c>
       <c r="D7" t="n">
-        <v>647</v>
+        <v>698</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="C8" t="n">
-        <v>1038</v>
+        <v>689</v>
       </c>
       <c r="D8" t="n">
-        <v>435</v>
+        <v>430</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C9" t="n">
-        <v>431</v>
+        <v>324</v>
       </c>
       <c r="D9" t="n">
-        <v>305</v>
+        <v>310</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>225</v>
+        <v>208</v>
       </c>
       <c r="D10" t="n">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -909,7 +909,7 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
         <v>203</v>
@@ -926,7 +926,7 @@
         <v>126</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>45</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1010,7 +1010,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1052,7 +1052,7 @@
         <v>97</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6713</v>
+        <v>4851</v>
       </c>
       <c r="C2" t="n">
-        <v>16196</v>
+        <v>10565</v>
       </c>
       <c r="D2" t="n">
-        <v>34050</v>
+        <v>47986</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3719</v>
+        <v>2637</v>
       </c>
       <c r="C3" t="n">
-        <v>8719</v>
+        <v>7419</v>
       </c>
       <c r="D3" t="n">
-        <v>16509</v>
+        <v>20745</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2885</v>
+        <v>2166</v>
       </c>
       <c r="C4" t="n">
-        <v>7862</v>
+        <v>5077</v>
       </c>
       <c r="D4" t="n">
-        <v>8340</v>
+        <v>11337</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2071</v>
+        <v>1645</v>
       </c>
       <c r="C5" t="n">
-        <v>5956</v>
+        <v>4046</v>
       </c>
       <c r="D5" t="n">
-        <v>3311</v>
+        <v>4553</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1237</v>
+        <v>1040</v>
       </c>
       <c r="C6" t="n">
-        <v>4381</v>
+        <v>3413</v>
       </c>
       <c r="D6" t="n">
-        <v>1338</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>606</v>
+        <v>525</v>
       </c>
       <c r="C7" t="n">
-        <v>2771</v>
+        <v>2121</v>
       </c>
       <c r="D7" t="n">
-        <v>713</v>
+        <v>787</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="C8" t="n">
-        <v>1502</v>
+        <v>1049</v>
       </c>
       <c r="D8" t="n">
-        <v>455</v>
+        <v>465</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C9" t="n">
-        <v>664</v>
+        <v>470</v>
       </c>
       <c r="D9" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10">
@@ -1206,10 +1206,10 @@
         <v>43</v>
       </c>
       <c r="C10" t="n">
-        <v>303</v>
+        <v>254</v>
       </c>
       <c r="D10" t="n">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
         <v>106</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1307,7 +1307,7 @@
         <v>39</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1363,7 +1363,7 @@
         <v>103</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7292</v>
+        <v>6379</v>
       </c>
       <c r="C2" t="n">
-        <v>13421</v>
+        <v>15896</v>
       </c>
       <c r="D2" t="n">
-        <v>30348</v>
+        <v>45493</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3939</v>
+        <v>2867</v>
       </c>
       <c r="C3" t="n">
-        <v>10426</v>
+        <v>7720</v>
       </c>
       <c r="D3" t="n">
-        <v>17443</v>
+        <v>22686</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2731</v>
+        <v>2034</v>
       </c>
       <c r="C4" t="n">
-        <v>7968</v>
+        <v>5934</v>
       </c>
       <c r="D4" t="n">
-        <v>9104</v>
+        <v>12238</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2117</v>
+        <v>1652</v>
       </c>
       <c r="C5" t="n">
-        <v>6525</v>
+        <v>4397</v>
       </c>
       <c r="D5" t="n">
-        <v>3854</v>
+        <v>5391</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1408</v>
+        <v>1166</v>
       </c>
       <c r="C6" t="n">
-        <v>4906</v>
+        <v>3604</v>
       </c>
       <c r="D6" t="n">
-        <v>1585</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>752</v>
+        <v>651</v>
       </c>
       <c r="C7" t="n">
-        <v>3385</v>
+        <v>2618</v>
       </c>
       <c r="D7" t="n">
-        <v>778</v>
+        <v>910</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>328</v>
+        <v>300</v>
       </c>
       <c r="C8" t="n">
-        <v>1946</v>
+        <v>1468</v>
       </c>
       <c r="D8" t="n">
-        <v>483</v>
+        <v>496</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C9" t="n">
-        <v>952</v>
+        <v>680</v>
       </c>
       <c r="D9" t="n">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="10">
@@ -1517,10 +1517,10 @@
         <v>52</v>
       </c>
       <c r="C10" t="n">
-        <v>423</v>
+        <v>329</v>
       </c>
       <c r="D10" t="n">
-        <v>252</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11">
@@ -1531,10 +1531,10 @@
         <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13">
@@ -1556,10 +1556,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
         <v>126</v>
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1618,7 +1618,7 @@
         <v>41</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1632,7 +1632,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6780</v>
+        <v>5744</v>
       </c>
       <c r="C2" t="n">
-        <v>9448</v>
+        <v>10936</v>
       </c>
       <c r="D2" t="n">
-        <v>25283</v>
+        <v>37483</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4743</v>
+        <v>3540</v>
       </c>
       <c r="C3" t="n">
-        <v>14816</v>
+        <v>11641</v>
       </c>
       <c r="D3" t="n">
-        <v>18624</v>
+        <v>24449</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1956</v>
+        <v>1526</v>
       </c>
       <c r="C4" t="n">
-        <v>10394</v>
+        <v>7468</v>
       </c>
       <c r="D4" t="n">
-        <v>8556</v>
+        <v>11715</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1300</v>
+        <v>1077</v>
       </c>
       <c r="C5" t="n">
-        <v>4807</v>
+        <v>3531</v>
       </c>
       <c r="D5" t="n">
-        <v>2552</v>
+        <v>3490</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>694</v>
+        <v>601</v>
       </c>
       <c r="C6" t="n">
-        <v>3317</v>
+        <v>2565</v>
       </c>
       <c r="D6" t="n">
-        <v>762</v>
+        <v>891</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>303</v>
+        <v>277</v>
       </c>
       <c r="C7" t="n">
-        <v>1907</v>
+        <v>1438</v>
       </c>
       <c r="D7" t="n">
-        <v>473</v>
+        <v>486</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C8" t="n">
-        <v>932</v>
+        <v>666</v>
       </c>
       <c r="D8" t="n">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="9">
@@ -1814,10 +1814,10 @@
         <v>48</v>
       </c>
       <c r="C9" t="n">
-        <v>414</v>
+        <v>322</v>
       </c>
       <c r="D9" t="n">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
     <row r="10">
@@ -1828,10 +1828,10 @@
         <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="D10" t="n">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" t="n">
         <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12">
@@ -1853,10 +1853,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
         <v>123</v>
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16">
@@ -1915,7 +1915,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
@@ -1929,7 +1929,7 @@
         <v>33</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4161</v>
+        <v>3380</v>
       </c>
       <c r="C2" t="n">
-        <v>4665</v>
+        <v>4895</v>
       </c>
       <c r="D2" t="n">
-        <v>17916</v>
+        <v>25764</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4809</v>
+        <v>3828</v>
       </c>
       <c r="C3" t="n">
-        <v>11384</v>
+        <v>10273</v>
       </c>
       <c r="D3" t="n">
-        <v>18433</v>
+        <v>25048</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2576</v>
+        <v>2013</v>
       </c>
       <c r="C4" t="n">
-        <v>12529</v>
+        <v>9522</v>
       </c>
       <c r="D4" t="n">
-        <v>9909</v>
+        <v>13305</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1452</v>
+        <v>1177</v>
       </c>
       <c r="C5" t="n">
-        <v>7037</v>
+        <v>5214</v>
       </c>
       <c r="D5" t="n">
-        <v>3215</v>
+        <v>4477</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>809</v>
+        <v>715</v>
       </c>
       <c r="C6" t="n">
-        <v>4006</v>
+        <v>3021</v>
       </c>
       <c r="D6" t="n">
-        <v>929</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="C7" t="n">
-        <v>2401</v>
+        <v>1862</v>
       </c>
       <c r="D7" t="n">
-        <v>516</v>
+        <v>541</v>
       </c>
     </row>
     <row r="8">
@@ -2111,10 +2111,10 @@
         <v>96</v>
       </c>
       <c r="C8" t="n">
-        <v>1221</v>
+        <v>883</v>
       </c>
       <c r="D8" t="n">
-        <v>330</v>
+        <v>335</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C9" t="n">
-        <v>442</v>
+        <v>367</v>
       </c>
       <c r="D9" t="n">
-        <v>255</v>
+        <v>258</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="D10" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D11" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D12" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
@@ -2212,7 +2212,7 @@
         <v>39</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2226,7 +2226,7 @@
         <v>32</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3695</v>
+        <v>2812</v>
       </c>
       <c r="C2" t="n">
-        <v>5028</v>
+        <v>10493</v>
       </c>
       <c r="D2" t="n">
-        <v>21208</v>
+        <v>26039</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3830</v>
+        <v>3059</v>
       </c>
       <c r="C3" t="n">
-        <v>7511</v>
+        <v>6928</v>
       </c>
       <c r="D3" t="n">
-        <v>17300</v>
+        <v>23462</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3002</v>
+        <v>2400</v>
       </c>
       <c r="C4" t="n">
-        <v>11740</v>
+        <v>9684</v>
       </c>
       <c r="D4" t="n">
-        <v>10917</v>
+        <v>14816</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1675</v>
+        <v>1358</v>
       </c>
       <c r="C5" t="n">
-        <v>9315</v>
+        <v>7090</v>
       </c>
       <c r="D5" t="n">
-        <v>4050</v>
+        <v>5696</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>979</v>
+        <v>829</v>
       </c>
       <c r="C6" t="n">
-        <v>5288</v>
+        <v>3990</v>
       </c>
       <c r="D6" t="n">
-        <v>1245</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>413</v>
+        <v>384</v>
       </c>
       <c r="C7" t="n">
-        <v>3044</v>
+        <v>2367</v>
       </c>
       <c r="D7" t="n">
-        <v>572</v>
+        <v>619</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C8" t="n">
-        <v>1683</v>
+        <v>1275</v>
       </c>
       <c r="D8" t="n">
-        <v>348</v>
+        <v>357</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>720</v>
+        <v>557</v>
       </c>
       <c r="D9" t="n">
-        <v>260</v>
+        <v>266</v>
       </c>
     </row>
     <row r="10">
@@ -2447,10 +2447,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>302</v>
+        <v>273</v>
       </c>
       <c r="D10" t="n">
         <v>212</v>
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D11" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2492,7 +2492,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D13" t="n">
         <v>100</v>
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -2523,7 +2523,7 @@
         <v>43</v>
       </c>
       <c r="D15" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2537,7 +2537,7 @@
         <v>34</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2276</v>
+        <v>1687</v>
       </c>
       <c r="C2" t="n">
-        <v>2486</v>
+        <v>5008</v>
       </c>
       <c r="D2" t="n">
-        <v>14979</v>
+        <v>18186</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3672</v>
+        <v>2923</v>
       </c>
       <c r="C3" t="n">
-        <v>6544</v>
+        <v>7897</v>
       </c>
       <c r="D3" t="n">
-        <v>17315</v>
+        <v>23204</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3272</v>
+        <v>2621</v>
       </c>
       <c r="C4" t="n">
-        <v>11364</v>
+        <v>9539</v>
       </c>
       <c r="D4" t="n">
-        <v>11677</v>
+        <v>15878</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1716</v>
+        <v>1427</v>
       </c>
       <c r="C5" t="n">
-        <v>11319</v>
+        <v>8760</v>
       </c>
       <c r="D5" t="n">
-        <v>4166</v>
+        <v>6014</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>761</v>
+        <v>684</v>
       </c>
       <c r="C6" t="n">
-        <v>5990</v>
+        <v>4697</v>
       </c>
       <c r="D6" t="n">
-        <v>1219</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C7" t="n">
-        <v>3110</v>
+        <v>2405</v>
       </c>
       <c r="D7" t="n">
-        <v>568</v>
+        <v>608</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C8" t="n">
-        <v>1183</v>
+        <v>920</v>
       </c>
       <c r="D8" t="n">
-        <v>368</v>
+        <v>378</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>295</v>
+        <v>267</v>
       </c>
       <c r="D9" t="n">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D10" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D11" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12">
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D12" t="n">
         <v>98</v>
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -2820,7 +2820,7 @@
         <v>42</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -2834,7 +2834,7 @@
         <v>33</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2742</v>
+        <v>2316</v>
       </c>
       <c r="C2" t="n">
-        <v>5229</v>
+        <v>10538</v>
       </c>
       <c r="D2" t="n">
-        <v>11943</v>
+        <v>15855</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2662</v>
+        <v>2083</v>
       </c>
       <c r="C3" t="n">
-        <v>4327</v>
+        <v>5941</v>
       </c>
       <c r="D3" t="n">
-        <v>16046</v>
+        <v>21039</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3025</v>
+        <v>2420</v>
       </c>
       <c r="C4" t="n">
-        <v>8999</v>
+        <v>8599</v>
       </c>
       <c r="D4" t="n">
-        <v>12133</v>
+        <v>16520</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2045</v>
+        <v>1682</v>
       </c>
       <c r="C5" t="n">
-        <v>11211</v>
+        <v>8998</v>
       </c>
       <c r="D5" t="n">
-        <v>5048</v>
+        <v>7251</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>987</v>
+        <v>863</v>
       </c>
       <c r="C6" t="n">
-        <v>8094</v>
+        <v>6339</v>
       </c>
       <c r="D6" t="n">
-        <v>1571</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>271</v>
+        <v>255</v>
       </c>
       <c r="C7" t="n">
-        <v>4242</v>
+        <v>3327</v>
       </c>
       <c r="D7" t="n">
-        <v>644</v>
+        <v>713</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C8" t="n">
-        <v>1847</v>
+        <v>1447</v>
       </c>
       <c r="D8" t="n">
-        <v>387</v>
+        <v>402</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>564</v>
+        <v>473</v>
       </c>
       <c r="D9" t="n">
-        <v>287</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="D10" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D12" t="n">
         <v>98</v>
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D13" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3131,7 +3131,7 @@
         <v>44</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -3145,7 +3145,7 @@
         <v>36</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1893</v>
+        <v>1605</v>
       </c>
       <c r="C2" t="n">
-        <v>3472</v>
+        <v>5255</v>
       </c>
       <c r="D2" t="n">
-        <v>10139</v>
+        <v>12433</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2357</v>
+        <v>1889</v>
       </c>
       <c r="C3" t="n">
-        <v>4249</v>
+        <v>7047</v>
       </c>
       <c r="D3" t="n">
-        <v>14739</v>
+        <v>19347</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2674</v>
+        <v>2125</v>
       </c>
       <c r="C4" t="n">
-        <v>7321</v>
+        <v>7564</v>
       </c>
       <c r="D4" t="n">
-        <v>12485</v>
+        <v>16740</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2216</v>
+        <v>1816</v>
       </c>
       <c r="C5" t="n">
-        <v>10578</v>
+        <v>9018</v>
       </c>
       <c r="D5" t="n">
-        <v>5623</v>
+        <v>8148</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1125</v>
+        <v>989</v>
       </c>
       <c r="C6" t="n">
-        <v>9308</v>
+        <v>7374</v>
       </c>
       <c r="D6" t="n">
-        <v>1850</v>
+        <v>2563</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="C7" t="n">
-        <v>5361</v>
+        <v>4232</v>
       </c>
       <c r="D7" t="n">
-        <v>723</v>
+        <v>809</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C8" t="n">
-        <v>2352</v>
+        <v>1859</v>
       </c>
       <c r="D8" t="n">
-        <v>392</v>
+        <v>417</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>600</v>
+        <v>524</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>289</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="D10" t="n">
-        <v>174</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D12" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
@@ -3428,7 +3428,7 @@
         <v>43</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3442,7 +3442,7 @@
         <v>35</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2834</v>
+        <v>1927</v>
       </c>
       <c r="C2" t="n">
-        <v>8393</v>
+        <v>7257</v>
       </c>
       <c r="D2" t="n">
-        <v>16433</v>
+        <v>12089</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1860</v>
+        <v>1511</v>
       </c>
       <c r="C3" t="n">
-        <v>3545</v>
+        <v>5689</v>
       </c>
       <c r="D3" t="n">
-        <v>13304</v>
+        <v>17365</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2234</v>
+        <v>1778</v>
       </c>
       <c r="C4" t="n">
-        <v>5959</v>
+        <v>7198</v>
       </c>
       <c r="D4" t="n">
-        <v>12408</v>
+        <v>16581</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2180</v>
+        <v>1770</v>
       </c>
       <c r="C5" t="n">
-        <v>9138</v>
+        <v>8272</v>
       </c>
       <c r="D5" t="n">
-        <v>6308</v>
+        <v>8894</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1342</v>
+        <v>1153</v>
       </c>
       <c r="C6" t="n">
-        <v>9686</v>
+        <v>7914</v>
       </c>
       <c r="D6" t="n">
-        <v>2261</v>
+        <v>3227</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>441</v>
+        <v>409</v>
       </c>
       <c r="C7" t="n">
-        <v>6712</v>
+        <v>5338</v>
       </c>
       <c r="D7" t="n">
-        <v>830</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C8" t="n">
-        <v>3347</v>
+        <v>2667</v>
       </c>
       <c r="D8" t="n">
-        <v>423</v>
+        <v>455</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>1114</v>
+        <v>929</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>324</v>
+        <v>305</v>
       </c>
       <c r="D10" t="n">
-        <v>180</v>
+        <v>189</v>
       </c>
     </row>
     <row r="11">
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
         <v>136</v>
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3753,7 +3753,7 @@
         <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4954</v>
+        <v>4307</v>
       </c>
       <c r="C2" t="n">
-        <v>11339</v>
+        <v>5086</v>
       </c>
       <c r="D2" t="n">
-        <v>13386</v>
+        <v>20949</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2093</v>
+        <v>1407</v>
       </c>
       <c r="C2" t="n">
-        <v>5035</v>
+        <v>4296</v>
       </c>
       <c r="D2" t="n">
-        <v>12357</v>
+        <v>8994</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2527</v>
+        <v>2016</v>
       </c>
       <c r="C3" t="n">
-        <v>4957</v>
+        <v>6603</v>
       </c>
       <c r="D3" t="n">
-        <v>14513</v>
+        <v>18620</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3156</v>
+        <v>2543</v>
       </c>
       <c r="C4" t="n">
-        <v>9002</v>
+        <v>10057</v>
       </c>
       <c r="D4" t="n">
-        <v>12533</v>
+        <v>16778</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1240</v>
+        <v>1081</v>
       </c>
       <c r="C5" t="n">
-        <v>13492</v>
+        <v>11521</v>
       </c>
       <c r="D5" t="n">
-        <v>5611</v>
+        <v>8016</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>407</v>
+        <v>377</v>
       </c>
       <c r="C6" t="n">
-        <v>8191</v>
+        <v>6627</v>
       </c>
       <c r="D6" t="n">
-        <v>1801</v>
+        <v>2418</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C7" t="n">
-        <v>3280</v>
+        <v>2613</v>
       </c>
       <c r="D7" t="n">
-        <v>512</v>
+        <v>564</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8" t="n">
-        <v>1091</v>
+        <v>910</v>
       </c>
       <c r="D8" t="n">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>317</v>
+        <v>298</v>
       </c>
       <c r="D9" t="n">
-        <v>176</v>
+        <v>185</v>
       </c>
     </row>
     <row r="10">
@@ -4316,7 +4316,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D10" t="n">
         <v>133</v>
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="D11" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D12" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
@@ -4361,7 +4361,7 @@
         <v>36</v>
       </c>
       <c r="D13" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6791</v>
+        <v>5890</v>
       </c>
       <c r="C2" t="n">
-        <v>4632</v>
+        <v>5181</v>
       </c>
       <c r="D2" t="n">
-        <v>12839</v>
+        <v>24287</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2106</v>
+        <v>1831</v>
       </c>
       <c r="C3" t="n">
-        <v>5714</v>
+        <v>2563</v>
       </c>
       <c r="D3" t="n">
-        <v>2888</v>
+        <v>4158</v>
       </c>
     </row>
     <row r="4">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C8" t="n">
         <v>260</v>
@@ -4610,7 +4610,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C9" t="n">
         <v>205</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4909</v>
+        <v>4029</v>
       </c>
       <c r="C2" t="n">
-        <v>6483</v>
+        <v>4843</v>
       </c>
       <c r="D2" t="n">
-        <v>19402</v>
+        <v>24188</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3649</v>
+        <v>3167</v>
       </c>
       <c r="C3" t="n">
-        <v>4399</v>
+        <v>3487</v>
       </c>
       <c r="D3" t="n">
-        <v>4347</v>
+        <v>7233</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>949</v>
+        <v>829</v>
       </c>
       <c r="C4" t="n">
-        <v>3392</v>
+        <v>1546</v>
       </c>
       <c r="D4" t="n">
-        <v>1763</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="5">
@@ -4907,7 +4907,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C8" t="n">
         <v>307</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5411</v>
+        <v>4026</v>
       </c>
       <c r="C2" t="n">
-        <v>10862</v>
+        <v>9072</v>
       </c>
       <c r="D2" t="n">
-        <v>19254</v>
+        <v>36145</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3509</v>
+        <v>2955</v>
       </c>
       <c r="C3" t="n">
-        <v>4791</v>
+        <v>3658</v>
       </c>
       <c r="D3" t="n">
-        <v>6442</v>
+        <v>9425</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1951</v>
+        <v>1696</v>
       </c>
       <c r="C4" t="n">
-        <v>3891</v>
+        <v>2613</v>
       </c>
       <c r="D4" t="n">
-        <v>2205</v>
+        <v>2958</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>442</v>
+        <v>394</v>
       </c>
       <c r="C5" t="n">
-        <v>1951</v>
+        <v>941</v>
       </c>
       <c r="D5" t="n">
-        <v>1253</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="6">
@@ -5193,7 +5193,7 @@
         <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="D6" t="n">
         <v>908</v>
@@ -5207,10 +5207,10 @@
         <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>620</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C8" t="n">
         <v>357</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>460</v>
       </c>
     </row>
     <row r="9">
@@ -5232,7 +5232,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C9" t="n">
         <v>268</v>
@@ -5249,7 +5249,7 @@
         <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5263,7 +5263,7 @@
         <v>46</v>
       </c>
       <c r="C11" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5305,7 +5305,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
         <v>148</v>
@@ -5319,7 +5319,7 @@
         <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D15" t="n">
         <v>120</v>
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6751</v>
+        <v>5159</v>
       </c>
       <c r="C2" t="n">
-        <v>8659</v>
+        <v>7515</v>
       </c>
       <c r="D2" t="n">
-        <v>34124</v>
+        <v>39631</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3605</v>
+        <v>2848</v>
       </c>
       <c r="C3" t="n">
-        <v>6889</v>
+        <v>5609</v>
       </c>
       <c r="D3" t="n">
-        <v>7935</v>
+        <v>12822</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2289</v>
+        <v>1978</v>
       </c>
       <c r="C4" t="n">
-        <v>4293</v>
+        <v>3120</v>
       </c>
       <c r="D4" t="n">
-        <v>2910</v>
+        <v>4047</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>980</v>
+        <v>854</v>
       </c>
       <c r="C5" t="n">
-        <v>2916</v>
+        <v>1779</v>
       </c>
       <c r="D5" t="n">
-        <v>1367</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>254</v>
+        <v>239</v>
       </c>
       <c r="C6" t="n">
-        <v>1120</v>
+        <v>623</v>
       </c>
       <c r="D6" t="n">
-        <v>955</v>
+        <v>963</v>
       </c>
     </row>
     <row r="7">
@@ -5521,7 +5521,7 @@
         <v>353</v>
       </c>
       <c r="D7" t="n">
-        <v>660</v>
+        <v>655</v>
       </c>
     </row>
     <row r="8">
@@ -5532,10 +5532,10 @@
         <v>130</v>
       </c>
       <c r="C8" t="n">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D8" t="n">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>377</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5574,7 +5574,7 @@
         <v>49</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D11" t="n">
         <v>286</v>
@@ -5588,7 +5588,7 @@
         <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D12" t="n">
         <v>217</v>
@@ -5616,7 +5616,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D14" t="n">
         <v>148</v>
@@ -5630,7 +5630,7 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
         <v>122</v>
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6985</v>
+        <v>5168</v>
       </c>
       <c r="C2" t="n">
-        <v>11276</v>
+        <v>5712</v>
       </c>
       <c r="D2" t="n">
-        <v>31110</v>
+        <v>31798</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3693</v>
+        <v>2880</v>
       </c>
       <c r="C3" t="n">
-        <v>6374</v>
+        <v>5392</v>
       </c>
       <c r="D3" t="n">
-        <v>10683</v>
+        <v>15047</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1804</v>
+        <v>1488</v>
       </c>
       <c r="C4" t="n">
-        <v>4630</v>
+        <v>3679</v>
       </c>
       <c r="D4" t="n">
-        <v>3260</v>
+        <v>4821</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>842</v>
+        <v>741</v>
       </c>
       <c r="C5" t="n">
-        <v>2648</v>
+        <v>1795</v>
       </c>
       <c r="D5" t="n">
-        <v>1278</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>290</v>
+        <v>257</v>
       </c>
       <c r="C6" t="n">
-        <v>1352</v>
+        <v>812</v>
       </c>
       <c r="D6" t="n">
-        <v>780</v>
+        <v>807</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C7" t="n">
-        <v>457</v>
+        <v>310</v>
       </c>
       <c r="D7" t="n">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="D9" t="n">
-        <v>273</v>
+        <v>269</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="12">
@@ -5902,7 +5902,7 @@
         <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13">
@@ -5913,7 +5913,7 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D13" t="n">
         <v>117</v>
@@ -5941,7 +5941,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6011,7 +6011,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
@@ -6028,7 +6028,7 @@
         <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5913</v>
+        <v>4479</v>
       </c>
       <c r="C2" t="n">
-        <v>8650</v>
+        <v>4748</v>
       </c>
       <c r="D2" t="n">
-        <v>28663</v>
+        <v>37931</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4416</v>
+        <v>3369</v>
       </c>
       <c r="C3" t="n">
-        <v>7918</v>
+        <v>4794</v>
       </c>
       <c r="D3" t="n">
-        <v>13328</v>
+        <v>16753</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2404</v>
+        <v>1897</v>
       </c>
       <c r="C4" t="n">
-        <v>5571</v>
+        <v>4638</v>
       </c>
       <c r="D4" t="n">
-        <v>4657</v>
+        <v>6689</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1165</v>
+        <v>995</v>
       </c>
       <c r="C5" t="n">
-        <v>3709</v>
+        <v>2860</v>
       </c>
       <c r="D5" t="n">
-        <v>1607</v>
+        <v>2156</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>523</v>
+        <v>458</v>
       </c>
       <c r="C6" t="n">
-        <v>2069</v>
+        <v>1358</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>936</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="C7" t="n">
-        <v>956</v>
+        <v>587</v>
       </c>
       <c r="D7" t="n">
-        <v>553</v>
+        <v>556</v>
       </c>
     </row>
     <row r="8">
@@ -6151,10 +6151,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C8" t="n">
-        <v>349</v>
+        <v>269</v>
       </c>
       <c r="D8" t="n">
         <v>385</v>
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D9" t="n">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13">
@@ -6227,7 +6227,7 @@
         <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14">
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6252,10 +6252,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6297,7 +6297,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6322,7 +6322,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6339,7 +6339,7 @@
         <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5290</v>
+        <v>3633</v>
       </c>
       <c r="C2" t="n">
-        <v>15277</v>
+        <v>9983</v>
       </c>
       <c r="D2" t="n">
-        <v>28110</v>
+        <v>39314</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4227</v>
+        <v>3219</v>
       </c>
       <c r="C3" t="n">
-        <v>7212</v>
+        <v>4127</v>
       </c>
       <c r="D3" t="n">
-        <v>14720</v>
+        <v>18935</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2911</v>
+        <v>2263</v>
       </c>
       <c r="C4" t="n">
-        <v>6685</v>
+        <v>4629</v>
       </c>
       <c r="D4" t="n">
-        <v>6052</v>
+        <v>8417</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1534</v>
+        <v>1256</v>
       </c>
       <c r="C5" t="n">
-        <v>4632</v>
+        <v>3773</v>
       </c>
       <c r="D5" t="n">
-        <v>2114</v>
+        <v>2896</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>759</v>
+        <v>659</v>
       </c>
       <c r="C6" t="n">
-        <v>2896</v>
+        <v>2135</v>
       </c>
       <c r="D6" t="n">
-        <v>972</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>298</v>
+        <v>268</v>
       </c>
       <c r="C7" t="n">
-        <v>1522</v>
+        <v>981</v>
       </c>
       <c r="D7" t="n">
-        <v>602</v>
+        <v>617</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C8" t="n">
-        <v>642</v>
+        <v>430</v>
       </c>
       <c r="D8" t="n">
-        <v>409</v>
+        <v>405</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>276</v>
+        <v>238</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13">
@@ -6535,7 +6535,7 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
         <v>121</v>
@@ -6552,7 +6552,7 @@
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -6566,7 +6566,7 @@
         <v>53</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -6608,7 +6608,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6630,10 +6630,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6650,7 +6650,7 @@
         <v>90</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_15_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_15_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3725</v>
+        <v>1270</v>
       </c>
       <c r="C2" t="n">
-        <v>11187</v>
+        <v>2859</v>
       </c>
       <c r="D2" t="n">
-        <v>32046</v>
+        <v>15375</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2816</v>
+        <v>2282</v>
       </c>
       <c r="C3" t="n">
-        <v>6135</v>
+        <v>6942</v>
       </c>
       <c r="D3" t="n">
-        <v>20566</v>
+        <v>11720</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2313</v>
+        <v>1642</v>
       </c>
       <c r="C4" t="n">
-        <v>4272</v>
+        <v>7991</v>
       </c>
       <c r="D4" t="n">
-        <v>9897</v>
+        <v>5147</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1521</v>
+        <v>857</v>
       </c>
       <c r="C5" t="n">
-        <v>4085</v>
+        <v>4557</v>
       </c>
       <c r="D5" t="n">
-        <v>3761</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>846</v>
+        <v>351</v>
       </c>
       <c r="C6" t="n">
-        <v>2914</v>
+        <v>1867</v>
       </c>
       <c r="D6" t="n">
-        <v>1403</v>
+        <v>736</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>400</v>
+        <v>106</v>
       </c>
       <c r="C7" t="n">
-        <v>1525</v>
+        <v>709</v>
       </c>
       <c r="D7" t="n">
-        <v>698</v>
+        <v>491</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>152</v>
+        <v>75</v>
       </c>
       <c r="C8" t="n">
-        <v>689</v>
+        <v>350</v>
       </c>
       <c r="D8" t="n">
-        <v>430</v>
+        <v>373</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>324</v>
+        <v>286</v>
       </c>
       <c r="D9" t="n">
-        <v>310</v>
+        <v>315</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="C10" t="n">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>269</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>142</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4851</v>
+        <v>2128</v>
       </c>
       <c r="C2" t="n">
-        <v>10565</v>
+        <v>2344</v>
       </c>
       <c r="D2" t="n">
-        <v>47986</v>
+        <v>14197</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2637</v>
+        <v>1518</v>
       </c>
       <c r="C3" t="n">
-        <v>7419</v>
+        <v>4192</v>
       </c>
       <c r="D3" t="n">
-        <v>20745</v>
+        <v>11573</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2166</v>
+        <v>1697</v>
       </c>
       <c r="C4" t="n">
-        <v>5077</v>
+        <v>7250</v>
       </c>
       <c r="D4" t="n">
-        <v>11337</v>
+        <v>6189</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1645</v>
+        <v>1090</v>
       </c>
       <c r="C5" t="n">
-        <v>4046</v>
+        <v>6319</v>
       </c>
       <c r="D5" t="n">
-        <v>4553</v>
+        <v>2395</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1040</v>
+        <v>521</v>
       </c>
       <c r="C6" t="n">
-        <v>3413</v>
+        <v>3207</v>
       </c>
       <c r="D6" t="n">
-        <v>1746</v>
+        <v>914</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>525</v>
+        <v>185</v>
       </c>
       <c r="C7" t="n">
-        <v>2121</v>
+        <v>1271</v>
       </c>
       <c r="D7" t="n">
-        <v>787</v>
+        <v>524</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>224</v>
+        <v>82</v>
       </c>
       <c r="C8" t="n">
-        <v>1049</v>
+        <v>515</v>
       </c>
       <c r="D8" t="n">
-        <v>465</v>
+        <v>390</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>87</v>
+        <v>57</v>
       </c>
       <c r="C9" t="n">
-        <v>470</v>
+        <v>318</v>
       </c>
       <c r="D9" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>217</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>177</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>94</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6379</v>
+        <v>1114</v>
       </c>
       <c r="C2" t="n">
-        <v>15896</v>
+        <v>976</v>
       </c>
       <c r="D2" t="n">
-        <v>45493</v>
+        <v>9565</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2867</v>
+        <v>1643</v>
       </c>
       <c r="C3" t="n">
-        <v>7720</v>
+        <v>3293</v>
       </c>
       <c r="D3" t="n">
-        <v>22686</v>
+        <v>11594</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2034</v>
+        <v>1842</v>
       </c>
       <c r="C4" t="n">
-        <v>5934</v>
+        <v>6591</v>
       </c>
       <c r="D4" t="n">
-        <v>12238</v>
+        <v>6918</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1652</v>
+        <v>1101</v>
       </c>
       <c r="C5" t="n">
-        <v>4397</v>
+        <v>7356</v>
       </c>
       <c r="D5" t="n">
-        <v>5391</v>
+        <v>2736</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1166</v>
+        <v>406</v>
       </c>
       <c r="C6" t="n">
-        <v>3604</v>
+        <v>4207</v>
       </c>
       <c r="D6" t="n">
-        <v>2083</v>
+        <v>933</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>651</v>
+        <v>75</v>
       </c>
       <c r="C7" t="n">
-        <v>2618</v>
+        <v>1227</v>
       </c>
       <c r="D7" t="n">
-        <v>910</v>
+        <v>555</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>300</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>1468</v>
+        <v>498</v>
       </c>
       <c r="D8" t="n">
-        <v>496</v>
+        <v>434</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>122</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>680</v>
+        <v>239</v>
       </c>
       <c r="D9" t="n">
-        <v>332</v>
+        <v>368</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>329</v>
+        <v>188</v>
       </c>
       <c r="D10" t="n">
-        <v>256</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>206</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>173</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>151</v>
+        <v>86</v>
       </c>
       <c r="D12" t="n">
-        <v>167</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>103</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>92</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5744</v>
+        <v>1453</v>
       </c>
       <c r="C2" t="n">
-        <v>10936</v>
+        <v>8946</v>
       </c>
       <c r="D2" t="n">
-        <v>37483</v>
+        <v>15259</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3540</v>
+        <v>1193</v>
       </c>
       <c r="C3" t="n">
-        <v>11641</v>
+        <v>1836</v>
       </c>
       <c r="D3" t="n">
-        <v>24449</v>
+        <v>10469</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1526</v>
+        <v>1541</v>
       </c>
       <c r="C4" t="n">
-        <v>7468</v>
+        <v>4744</v>
       </c>
       <c r="D4" t="n">
-        <v>11715</v>
+        <v>7627</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1077</v>
+        <v>1294</v>
       </c>
       <c r="C5" t="n">
-        <v>3531</v>
+        <v>6954</v>
       </c>
       <c r="D5" t="n">
-        <v>3490</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="C6" t="n">
-        <v>2565</v>
+        <v>5686</v>
       </c>
       <c r="D6" t="n">
-        <v>891</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>277</v>
+        <v>167</v>
       </c>
       <c r="C7" t="n">
-        <v>1438</v>
+        <v>2593</v>
       </c>
       <c r="D7" t="n">
-        <v>486</v>
+        <v>610</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C8" t="n">
-        <v>666</v>
+        <v>812</v>
       </c>
       <c r="D8" t="n">
-        <v>325</v>
+        <v>449</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="C9" t="n">
-        <v>322</v>
+        <v>339</v>
       </c>
       <c r="D9" t="n">
-        <v>250</v>
+        <v>374</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="D10" t="n">
-        <v>200</v>
+        <v>227</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>163</v>
+        <v>178</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="D12" t="n">
-        <v>123</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>77</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>89</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>102</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3380</v>
+        <v>739</v>
       </c>
       <c r="C2" t="n">
-        <v>4895</v>
+        <v>4133</v>
       </c>
       <c r="D2" t="n">
-        <v>25764</v>
+        <v>10693</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3828</v>
+        <v>1127</v>
       </c>
       <c r="C3" t="n">
-        <v>10273</v>
+        <v>4548</v>
       </c>
       <c r="D3" t="n">
-        <v>25048</v>
+        <v>10517</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2013</v>
+        <v>1311</v>
       </c>
       <c r="C4" t="n">
-        <v>9522</v>
+        <v>3414</v>
       </c>
       <c r="D4" t="n">
-        <v>13305</v>
+        <v>7904</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1177</v>
+        <v>1348</v>
       </c>
       <c r="C5" t="n">
-        <v>5214</v>
+        <v>6142</v>
       </c>
       <c r="D5" t="n">
-        <v>4477</v>
+        <v>3874</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>715</v>
+        <v>768</v>
       </c>
       <c r="C6" t="n">
-        <v>3021</v>
+        <v>6437</v>
       </c>
       <c r="D6" t="n">
-        <v>1155</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>260</v>
+        <v>189</v>
       </c>
       <c r="C7" t="n">
-        <v>1862</v>
+        <v>3679</v>
       </c>
       <c r="D7" t="n">
-        <v>541</v>
+        <v>666</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>96</v>
+        <v>53</v>
       </c>
       <c r="C8" t="n">
-        <v>883</v>
+        <v>1249</v>
       </c>
       <c r="D8" t="n">
-        <v>335</v>
+        <v>482</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>367</v>
+        <v>446</v>
       </c>
       <c r="D9" t="n">
-        <v>258</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="D10" t="n">
-        <v>210</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>186</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>87</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>99</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2812</v>
+        <v>767</v>
       </c>
       <c r="C2" t="n">
-        <v>10493</v>
+        <v>9154</v>
       </c>
       <c r="D2" t="n">
-        <v>26039</v>
+        <v>13329</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3059</v>
+        <v>814</v>
       </c>
       <c r="C3" t="n">
-        <v>6928</v>
+        <v>3825</v>
       </c>
       <c r="D3" t="n">
-        <v>23462</v>
+        <v>9834</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2400</v>
+        <v>1075</v>
       </c>
       <c r="C4" t="n">
-        <v>9684</v>
+        <v>3898</v>
       </c>
       <c r="D4" t="n">
-        <v>14816</v>
+        <v>8090</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1358</v>
+        <v>1232</v>
       </c>
       <c r="C5" t="n">
-        <v>7090</v>
+        <v>4789</v>
       </c>
       <c r="D5" t="n">
-        <v>5696</v>
+        <v>4375</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>829</v>
+        <v>923</v>
       </c>
       <c r="C6" t="n">
-        <v>3990</v>
+        <v>6244</v>
       </c>
       <c r="D6" t="n">
-        <v>1618</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>384</v>
+        <v>356</v>
       </c>
       <c r="C7" t="n">
-        <v>2367</v>
+        <v>4902</v>
       </c>
       <c r="D7" t="n">
-        <v>619</v>
+        <v>765</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>134</v>
+        <v>88</v>
       </c>
       <c r="C8" t="n">
-        <v>1275</v>
+        <v>2237</v>
       </c>
       <c r="D8" t="n">
-        <v>357</v>
+        <v>500</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="C9" t="n">
-        <v>557</v>
+        <v>749</v>
       </c>
       <c r="D9" t="n">
-        <v>266</v>
+        <v>381</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>273</v>
+        <v>306</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
         <v>182</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>188</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>101</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1687</v>
+        <v>515</v>
       </c>
       <c r="C2" t="n">
-        <v>5008</v>
+        <v>4761</v>
       </c>
       <c r="D2" t="n">
-        <v>18186</v>
+        <v>9596</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2923</v>
+        <v>1084</v>
       </c>
       <c r="C3" t="n">
-        <v>7897</v>
+        <v>5610</v>
       </c>
       <c r="D3" t="n">
-        <v>23204</v>
+        <v>10800</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2621</v>
+        <v>1670</v>
       </c>
       <c r="C4" t="n">
-        <v>9539</v>
+        <v>5561</v>
       </c>
       <c r="D4" t="n">
-        <v>15878</v>
+        <v>8438</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1427</v>
+        <v>943</v>
       </c>
       <c r="C5" t="n">
-        <v>8760</v>
+        <v>7930</v>
       </c>
       <c r="D5" t="n">
-        <v>6014</v>
+        <v>4068</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>684</v>
+        <v>328</v>
       </c>
       <c r="C6" t="n">
-        <v>4697</v>
+        <v>6394</v>
       </c>
       <c r="D6" t="n">
-        <v>1562</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>123</v>
+        <v>81</v>
       </c>
       <c r="C7" t="n">
-        <v>2405</v>
+        <v>2192</v>
       </c>
       <c r="D7" t="n">
-        <v>608</v>
+        <v>602</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="C8" t="n">
-        <v>920</v>
+        <v>734</v>
       </c>
       <c r="D8" t="n">
-        <v>378</v>
+        <v>373</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>267</v>
+        <v>299</v>
       </c>
       <c r="D9" t="n">
-        <v>285</v>
+        <v>244</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
         <v>178</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>87</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2316</v>
+        <v>358</v>
       </c>
       <c r="C2" t="n">
-        <v>10538</v>
+        <v>2582</v>
       </c>
       <c r="D2" t="n">
-        <v>15855</v>
+        <v>7255</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2083</v>
+        <v>718</v>
       </c>
       <c r="C3" t="n">
-        <v>5941</v>
+        <v>4559</v>
       </c>
       <c r="D3" t="n">
-        <v>21039</v>
+        <v>9852</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2420</v>
+        <v>1161</v>
       </c>
       <c r="C4" t="n">
-        <v>8599</v>
+        <v>5305</v>
       </c>
       <c r="D4" t="n">
-        <v>16520</v>
+        <v>8233</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1682</v>
+        <v>891</v>
       </c>
       <c r="C5" t="n">
-        <v>8998</v>
+        <v>6036</v>
       </c>
       <c r="D5" t="n">
-        <v>7251</v>
+        <v>4195</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>863</v>
+        <v>331</v>
       </c>
       <c r="C6" t="n">
-        <v>6339</v>
+        <v>5825</v>
       </c>
       <c r="D6" t="n">
-        <v>2155</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>255</v>
+        <v>72</v>
       </c>
       <c r="C7" t="n">
-        <v>3327</v>
+        <v>2922</v>
       </c>
       <c r="D7" t="n">
-        <v>713</v>
+        <v>586</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>1447</v>
+        <v>844</v>
       </c>
       <c r="D8" t="n">
-        <v>402</v>
+        <v>324</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>473</v>
+        <v>281</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>196</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>205</v>
+        <v>132</v>
       </c>
       <c r="D10" t="n">
-        <v>175</v>
+        <v>141</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>76</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1605</v>
+        <v>361</v>
       </c>
       <c r="C2" t="n">
-        <v>5255</v>
+        <v>4094</v>
       </c>
       <c r="D2" t="n">
-        <v>12433</v>
+        <v>8575</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1889</v>
+        <v>458</v>
       </c>
       <c r="C3" t="n">
-        <v>7047</v>
+        <v>3013</v>
       </c>
       <c r="D3" t="n">
-        <v>19347</v>
+        <v>8727</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2125</v>
+        <v>827</v>
       </c>
       <c r="C4" t="n">
-        <v>7564</v>
+        <v>4772</v>
       </c>
       <c r="D4" t="n">
-        <v>16740</v>
+        <v>8293</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1816</v>
+        <v>924</v>
       </c>
       <c r="C5" t="n">
-        <v>9018</v>
+        <v>5568</v>
       </c>
       <c r="D5" t="n">
-        <v>8148</v>
+        <v>4804</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>989</v>
+        <v>537</v>
       </c>
       <c r="C6" t="n">
-        <v>7374</v>
+        <v>5926</v>
       </c>
       <c r="D6" t="n">
-        <v>2563</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>229</v>
+        <v>164</v>
       </c>
       <c r="C7" t="n">
-        <v>4232</v>
+        <v>4371</v>
       </c>
       <c r="D7" t="n">
-        <v>809</v>
+        <v>752</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="C8" t="n">
-        <v>1859</v>
+        <v>1849</v>
       </c>
       <c r="D8" t="n">
-        <v>417</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>524</v>
+        <v>537</v>
       </c>
       <c r="D9" t="n">
-        <v>289</v>
+        <v>214</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>213</v>
+        <v>197</v>
       </c>
       <c r="D10" t="n">
-        <v>180</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>128</v>
+        <v>98</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1927</v>
+        <v>267</v>
       </c>
       <c r="C2" t="n">
-        <v>7257</v>
+        <v>7803</v>
       </c>
       <c r="D2" t="n">
-        <v>12089</v>
+        <v>14513</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1511</v>
+        <v>344</v>
       </c>
       <c r="C3" t="n">
-        <v>5689</v>
+        <v>3099</v>
       </c>
       <c r="D3" t="n">
-        <v>17365</v>
+        <v>8104</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1778</v>
+        <v>577</v>
       </c>
       <c r="C4" t="n">
-        <v>7198</v>
+        <v>3760</v>
       </c>
       <c r="D4" t="n">
-        <v>16581</v>
+        <v>8036</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1770</v>
+        <v>806</v>
       </c>
       <c r="C5" t="n">
-        <v>8272</v>
+        <v>5054</v>
       </c>
       <c r="D5" t="n">
-        <v>8894</v>
+        <v>5260</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1153</v>
+        <v>647</v>
       </c>
       <c r="C6" t="n">
-        <v>7914</v>
+        <v>5692</v>
       </c>
       <c r="D6" t="n">
-        <v>3227</v>
+        <v>2465</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>409</v>
+        <v>292</v>
       </c>
       <c r="C7" t="n">
-        <v>5338</v>
+        <v>5057</v>
       </c>
       <c r="D7" t="n">
-        <v>1007</v>
+        <v>939</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="C8" t="n">
-        <v>2667</v>
+        <v>3009</v>
       </c>
       <c r="D8" t="n">
-        <v>455</v>
+        <v>418</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>929</v>
+        <v>1115</v>
       </c>
       <c r="D9" t="n">
-        <v>298</v>
+        <v>233</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>305</v>
+        <v>340</v>
       </c>
       <c r="D10" t="n">
-        <v>189</v>
+        <v>153</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>65</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4307</v>
+        <v>5629</v>
       </c>
       <c r="C2" t="n">
-        <v>5086</v>
+        <v>9549</v>
       </c>
       <c r="D2" t="n">
-        <v>20949</v>
+        <v>12735</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1407</v>
+        <v>403</v>
       </c>
       <c r="C2" t="n">
-        <v>4296</v>
+        <v>9016</v>
       </c>
       <c r="D2" t="n">
-        <v>8994</v>
+        <v>14058</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2016</v>
+        <v>260</v>
       </c>
       <c r="C3" t="n">
-        <v>6603</v>
+        <v>4576</v>
       </c>
       <c r="D3" t="n">
-        <v>18620</v>
+        <v>8431</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2543</v>
+        <v>420</v>
       </c>
       <c r="C4" t="n">
-        <v>10057</v>
+        <v>3370</v>
       </c>
       <c r="D4" t="n">
-        <v>16778</v>
+        <v>7802</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1081</v>
+        <v>653</v>
       </c>
       <c r="C5" t="n">
-        <v>11521</v>
+        <v>4316</v>
       </c>
       <c r="D5" t="n">
-        <v>8016</v>
+        <v>5475</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>377</v>
+        <v>665</v>
       </c>
       <c r="C6" t="n">
-        <v>6627</v>
+        <v>5355</v>
       </c>
       <c r="D6" t="n">
-        <v>2418</v>
+        <v>2861</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>77</v>
+        <v>390</v>
       </c>
       <c r="C7" t="n">
-        <v>2613</v>
+        <v>5279</v>
       </c>
       <c r="D7" t="n">
-        <v>564</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>142</v>
       </c>
       <c r="C8" t="n">
-        <v>910</v>
+        <v>3870</v>
       </c>
       <c r="D8" t="n">
-        <v>292</v>
+        <v>481</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="C9" t="n">
-        <v>298</v>
+        <v>1875</v>
       </c>
       <c r="D9" t="n">
-        <v>185</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>147</v>
+        <v>632</v>
       </c>
       <c r="D10" t="n">
-        <v>133</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>86</v>
+        <v>213</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>97</v>
       </c>
       <c r="D12" t="n">
-        <v>61</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="D13" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5890</v>
+        <v>6089</v>
       </c>
       <c r="C2" t="n">
-        <v>5181</v>
+        <v>8549</v>
       </c>
       <c r="D2" t="n">
-        <v>24287</v>
+        <v>15457</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1831</v>
+        <v>1859</v>
       </c>
       <c r="C3" t="n">
-        <v>2563</v>
+        <v>3770</v>
       </c>
       <c r="D3" t="n">
-        <v>4158</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>385</v>
+        <v>334</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>454</v>
+        <v>360</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4029</v>
+        <v>3640</v>
       </c>
       <c r="C2" t="n">
-        <v>4843</v>
+        <v>5374</v>
       </c>
       <c r="D2" t="n">
-        <v>24188</v>
+        <v>20432</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3167</v>
+        <v>3359</v>
       </c>
       <c r="C3" t="n">
-        <v>3487</v>
+        <v>5712</v>
       </c>
       <c r="D3" t="n">
-        <v>7233</v>
+        <v>4481</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>829</v>
+        <v>884</v>
       </c>
       <c r="C4" t="n">
-        <v>1546</v>
+        <v>2400</v>
       </c>
       <c r="D4" t="n">
-        <v>2019</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>135</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>343</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>406</v>
+        <v>324</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>116</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>244</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4026</v>
+        <v>2084</v>
       </c>
       <c r="C2" t="n">
-        <v>9072</v>
+        <v>6155</v>
       </c>
       <c r="D2" t="n">
-        <v>36145</v>
+        <v>15927</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2955</v>
+        <v>2887</v>
       </c>
       <c r="C3" t="n">
-        <v>3658</v>
+        <v>4749</v>
       </c>
       <c r="D3" t="n">
-        <v>9425</v>
+        <v>6830</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1696</v>
+        <v>1864</v>
       </c>
       <c r="C4" t="n">
-        <v>2613</v>
+        <v>4321</v>
       </c>
       <c r="D4" t="n">
-        <v>2958</v>
+        <v>2126</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>394</v>
+        <v>424</v>
       </c>
       <c r="C5" t="n">
-        <v>941</v>
+        <v>1465</v>
       </c>
       <c r="D5" t="n">
-        <v>1299</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>110</v>
       </c>
       <c r="C6" t="n">
-        <v>301</v>
+        <v>262</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>794</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>116</v>
       </c>
       <c r="C7" t="n">
-        <v>407</v>
+        <v>334</v>
       </c>
       <c r="D7" t="n">
-        <v>620</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>126</v>
+        <v>91</v>
       </c>
       <c r="C8" t="n">
-        <v>357</v>
+        <v>286</v>
       </c>
       <c r="D8" t="n">
-        <v>460</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>216</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>208</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>194</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5159</v>
+        <v>2263</v>
       </c>
       <c r="C2" t="n">
-        <v>7515</v>
+        <v>5495</v>
       </c>
       <c r="D2" t="n">
-        <v>39631</v>
+        <v>15396</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2848</v>
+        <v>2088</v>
       </c>
       <c r="C3" t="n">
-        <v>5609</v>
+        <v>4774</v>
       </c>
       <c r="D3" t="n">
-        <v>12822</v>
+        <v>7793</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1978</v>
+        <v>2031</v>
       </c>
       <c r="C4" t="n">
-        <v>3120</v>
+        <v>4473</v>
       </c>
       <c r="D4" t="n">
-        <v>4047</v>
+        <v>2964</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>854</v>
+        <v>973</v>
       </c>
       <c r="C5" t="n">
-        <v>1779</v>
+        <v>2983</v>
       </c>
       <c r="D5" t="n">
-        <v>1533</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C6" t="n">
-        <v>623</v>
+        <v>905</v>
       </c>
       <c r="D6" t="n">
-        <v>963</v>
+        <v>840</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>105</v>
       </c>
       <c r="C7" t="n">
-        <v>353</v>
+        <v>295</v>
       </c>
       <c r="D7" t="n">
-        <v>655</v>
+        <v>585</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="C8" t="n">
-        <v>377</v>
+        <v>310</v>
       </c>
       <c r="D8" t="n">
-        <v>481</v>
+        <v>422</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="C9" t="n">
-        <v>309</v>
+        <v>250</v>
       </c>
       <c r="D9" t="n">
-        <v>377</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>313</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>188</v>
+        <v>160</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>254</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5168</v>
+        <v>3154</v>
       </c>
       <c r="C2" t="n">
-        <v>5712</v>
+        <v>9189</v>
       </c>
       <c r="D2" t="n">
-        <v>31798</v>
+        <v>16872</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2880</v>
+        <v>1793</v>
       </c>
       <c r="C3" t="n">
-        <v>5392</v>
+        <v>4478</v>
       </c>
       <c r="D3" t="n">
-        <v>15047</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1488</v>
+        <v>1787</v>
       </c>
       <c r="C4" t="n">
-        <v>3679</v>
+        <v>4541</v>
       </c>
       <c r="D4" t="n">
-        <v>4821</v>
+        <v>3754</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>741</v>
+        <v>1282</v>
       </c>
       <c r="C5" t="n">
-        <v>1795</v>
+        <v>3664</v>
       </c>
       <c r="D5" t="n">
-        <v>1543</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>257</v>
+        <v>522</v>
       </c>
       <c r="C6" t="n">
-        <v>812</v>
+        <v>1952</v>
       </c>
       <c r="D6" t="n">
-        <v>807</v>
+        <v>899</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>85</v>
+        <v>149</v>
       </c>
       <c r="C7" t="n">
-        <v>310</v>
+        <v>599</v>
       </c>
       <c r="D7" t="n">
-        <v>512</v>
+        <v>615</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="C8" t="n">
-        <v>221</v>
+        <v>302</v>
       </c>
       <c r="D8" t="n">
-        <v>361</v>
+        <v>444</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="C9" t="n">
-        <v>199</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>269</v>
+        <v>347</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>216</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>260</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>145</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>205</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>119</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4479</v>
+        <v>2716</v>
       </c>
       <c r="C2" t="n">
-        <v>4748</v>
+        <v>10438</v>
       </c>
       <c r="D2" t="n">
-        <v>37931</v>
+        <v>28675</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3369</v>
+        <v>1965</v>
       </c>
       <c r="C3" t="n">
-        <v>4794</v>
+        <v>5916</v>
       </c>
       <c r="D3" t="n">
-        <v>16753</v>
+        <v>9042</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1897</v>
+        <v>1539</v>
       </c>
       <c r="C4" t="n">
-        <v>4638</v>
+        <v>4414</v>
       </c>
       <c r="D4" t="n">
-        <v>6689</v>
+        <v>4442</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>995</v>
+        <v>1353</v>
       </c>
       <c r="C5" t="n">
-        <v>2860</v>
+        <v>3981</v>
       </c>
       <c r="D5" t="n">
-        <v>2156</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>458</v>
+        <v>775</v>
       </c>
       <c r="C6" t="n">
-        <v>1358</v>
+        <v>2753</v>
       </c>
       <c r="D6" t="n">
-        <v>936</v>
+        <v>984</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>156</v>
+        <v>278</v>
       </c>
       <c r="C7" t="n">
-        <v>587</v>
+        <v>1235</v>
       </c>
       <c r="D7" t="n">
-        <v>556</v>
+        <v>647</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>66</v>
+        <v>106</v>
       </c>
       <c r="C8" t="n">
-        <v>269</v>
+        <v>435</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>466</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>77</v>
       </c>
       <c r="C9" t="n">
-        <v>210</v>
+        <v>284</v>
       </c>
       <c r="D9" t="n">
-        <v>282</v>
+        <v>357</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>241</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>308</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>190</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>264</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>154</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>207</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>128</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>102</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>94</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3633</v>
+        <v>2490</v>
       </c>
       <c r="C2" t="n">
-        <v>9983</v>
+        <v>6429</v>
       </c>
       <c r="D2" t="n">
-        <v>39314</v>
+        <v>22425</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3219</v>
+        <v>2667</v>
       </c>
       <c r="C3" t="n">
-        <v>4127</v>
+        <v>9083</v>
       </c>
       <c r="D3" t="n">
-        <v>18935</v>
+        <v>10431</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2263</v>
+        <v>1250</v>
       </c>
       <c r="C4" t="n">
-        <v>4629</v>
+        <v>6576</v>
       </c>
       <c r="D4" t="n">
-        <v>8417</v>
+        <v>4222</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1256</v>
+        <v>716</v>
       </c>
       <c r="C5" t="n">
-        <v>3773</v>
+        <v>2697</v>
       </c>
       <c r="D5" t="n">
-        <v>2896</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>659</v>
+        <v>256</v>
       </c>
       <c r="C6" t="n">
-        <v>2135</v>
+        <v>1210</v>
       </c>
       <c r="D6" t="n">
-        <v>1145</v>
+        <v>634</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>268</v>
+        <v>97</v>
       </c>
       <c r="C7" t="n">
-        <v>981</v>
+        <v>426</v>
       </c>
       <c r="D7" t="n">
-        <v>617</v>
+        <v>456</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="C8" t="n">
-        <v>430</v>
+        <v>278</v>
       </c>
       <c r="D8" t="n">
-        <v>405</v>
+        <v>349</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>258</v>
       </c>
     </row>
     <row r="11">
@@ -6504,10 +6504,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
         <v>202</v>
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>92</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>145</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
